--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\OH\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9B1C938-82A1-4920-A509-CF0DA5E4BEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{206F325F-35DD-4C3C-9779-E154AA1B4C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10865" windowHeight="10080" firstSheet="1" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
+    <workbookView xWindow="1430" yWindow="720" windowWidth="14480" windowHeight="10080" firstSheet="1" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -604,9 +604,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667665C7-8A8E-46D9-B686-64BA7741F669}">
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -614,20 +614,20 @@
         <v>63</v>
       </c>
       <c r="C1" s="3">
-        <v>45238</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -635,147 +635,147 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>62</v>
       </c>
@@ -792,12 +792,12 @@
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.54296875" customWidth="1"/>
+    <col min="1" max="1" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -805,7 +805,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -813,7 +813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -821,7 +821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -829,7 +829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -845,7 +845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -853,7 +853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -861,7 +861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -869,7 +869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -877,7 +877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -885,7 +885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -893,7 +893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -901,7 +901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -909,7 +909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -917,7 +917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -925,7 +925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -933,7 +933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -941,7 +941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -949,7 +949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -957,7 +957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -965,7 +965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -973,7 +973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -1008,13 +1008,13 @@
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.54296875" customWidth="1"/>
-    <col min="2" max="2" width="19.1328125" customWidth="1"/>
+    <col min="1" max="1" width="34.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -1041,9 +1041,9 @@
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>49</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>48</v>
       </c>
